--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,6 +1285,3751 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128566784</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>537255</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983933</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128563380</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>537130</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983903</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128563099</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>537112</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6983914</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128562997</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>537107</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6983905</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128567714</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>537314</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6983876</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128567670</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>537282</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6983918</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128566920</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>537279</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6983922</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128563814</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>537147</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6983935</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128567589</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>537289</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6983869</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128564364</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>537169</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6983991</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128565305</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>537228</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6983979</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128567077</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>537265</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6983926</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128568010</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>537223</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6983867</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128568394</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>537178</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6983855</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128563551</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>537139</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6983908</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128567544</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>537293</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6983882</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128564408</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>537155</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6983961</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128567227</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>537292</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6983911</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128564188</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>537140</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6983933</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128562753</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>537089</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6983899</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128566515</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>537248</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6983943</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128565676</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>537263</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6983976</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128562964</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>537107</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6983905</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128564240</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>537145</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6983943</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128562925</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>537100</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6983903</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128565808</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>537271</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6983985</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128563502</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>537130</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6983903</v>
+      </c>
+      <c r="S34" t="n">
+        <v>30</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128565042</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>537218</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6983991</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128564077</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>537145</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6983958</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128566475</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>537259</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6983948</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128563582</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>537142</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6983916</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128567506</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>537276</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6983912</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128568213</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>537231</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6983882</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128567360</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>537297</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6983900</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128564451</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>537157</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6983973</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B8" t="n">
         <v>98571</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R8" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B9" t="n">
         <v>98571</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R9" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B10" t="n">
         <v>98571</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R10" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B11" t="n">
         <v>98571</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R11" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R16" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R17" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3106,32 +3106,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128567227</v>
+        <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537292</v>
+        <v>537140</v>
       </c>
       <c r="R25" t="n">
-        <v>6983911</v>
+        <v>6983933</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128564188</v>
+        <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537140</v>
+        <v>537292</v>
       </c>
       <c r="R26" t="n">
-        <v>6983933</v>
+        <v>6983911</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B27" t="n">
         <v>98571</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R27" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B28" t="n">
         <v>98571</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R28" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128564240</v>
+        <v>128562925</v>
       </c>
       <c r="B31" t="n">
         <v>98571</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537145</v>
+        <v>537100</v>
       </c>
       <c r="R31" t="n">
-        <v>6983943</v>
+        <v>6983903</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128562925</v>
+        <v>128565808</v>
       </c>
       <c r="B32" t="n">
         <v>98571</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537100</v>
+        <v>537271</v>
       </c>
       <c r="R32" t="n">
-        <v>6983903</v>
+        <v>6983985</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565808</v>
+        <v>128564240</v>
       </c>
       <c r="B33" t="n">
         <v>98571</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537271</v>
+        <v>537145</v>
       </c>
       <c r="R33" t="n">
-        <v>6983985</v>
+        <v>6983943</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128563502</v>
+        <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>57845</v>
+        <v>80188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537130</v>
+        <v>537145</v>
       </c>
       <c r="R34" t="n">
-        <v>6983903</v>
+        <v>6983958</v>
       </c>
       <c r="S34" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R35" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128564077</v>
+        <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537145</v>
+        <v>537218</v>
       </c>
       <c r="R36" t="n">
-        <v>6983958</v>
+        <v>6983991</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B37" t="n">
         <v>98571</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R37" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B38" t="n">
         <v>98571</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R38" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567506</v>
+        <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537276</v>
+        <v>537297</v>
       </c>
       <c r="R39" t="n">
-        <v>6983912</v>
+        <v>6983900</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567360</v>
+        <v>128567506</v>
       </c>
       <c r="B41" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537297</v>
+        <v>537276</v>
       </c>
       <c r="R41" t="n">
-        <v>6983900</v>
+        <v>6983912</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R13" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R14" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R8" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R9" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R10" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R11" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R13" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R14" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B18" t="n">
-        <v>80188</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R18" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R19" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,7 +3002,7 @@
         <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R27" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R28" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128562964</v>
       </c>
       <c r="B29" t="n">
-        <v>80188</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537107</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983905</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128564240</v>
       </c>
       <c r="B30" t="n">
-        <v>57845</v>
+        <v>98579</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537145</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983943</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,7 +3751,7 @@
         <v>128562925</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128564240</v>
+        <v>128565676</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537145</v>
+        <v>537263</v>
       </c>
       <c r="R33" t="n">
-        <v>6983943</v>
+        <v>6983976</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,7 +4072,7 @@
         <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128563502</v>
+        <v>128565042</v>
       </c>
       <c r="B35" t="n">
-        <v>57845</v>
+        <v>98579</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537130</v>
+        <v>537218</v>
       </c>
       <c r="R35" t="n">
-        <v>6983903</v>
+        <v>6983991</v>
       </c>
       <c r="S35" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>57849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R36" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R37" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R38" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,7 +4607,7 @@
         <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128568213</v>
+        <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537231</v>
+        <v>537276</v>
       </c>
       <c r="R40" t="n">
-        <v>6983882</v>
+        <v>6983912</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R41" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R8" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R9" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R10" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R11" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R16" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>80192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R17" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R18" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R19" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R27" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B28" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R28" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>80192</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128564240</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>98579</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537145</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983943</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,7 +3751,7 @@
         <v>128562925</v>
       </c>
       <c r="B31" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565676</v>
+        <v>128564240</v>
       </c>
       <c r="B33" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537263</v>
+        <v>537145</v>
       </c>
       <c r="R33" t="n">
-        <v>6983976</v>
+        <v>6983943</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>98579</v>
+        <v>57849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R35" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128563502</v>
+        <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537130</v>
+        <v>537218</v>
       </c>
       <c r="R36" t="n">
-        <v>6983903</v>
+        <v>6983991</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B37" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R37" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B38" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R38" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B40" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R40" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568213</v>
+        <v>128567506</v>
       </c>
       <c r="B41" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537231</v>
+        <v>537276</v>
       </c>
       <c r="R41" t="n">
-        <v>6983882</v>
+        <v>6983912</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128564077</v>
+        <v>128565042</v>
       </c>
       <c r="B34" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537145</v>
+        <v>537218</v>
       </c>
       <c r="R34" t="n">
-        <v>6983958</v>
+        <v>6983991</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128563502</v>
+        <v>128564077</v>
       </c>
       <c r="B35" t="n">
-        <v>57849</v>
+        <v>80192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537130</v>
+        <v>537145</v>
       </c>
       <c r="R35" t="n">
-        <v>6983903</v>
+        <v>6983958</v>
       </c>
       <c r="S35" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R36" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R8" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R9" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R10" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R11" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R16" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>80192</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R17" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,7 +2360,7 @@
         <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R27" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R28" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128562964</v>
       </c>
       <c r="B29" t="n">
-        <v>80192</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537107</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983905</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128564240</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537145</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983943</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,7 +3751,7 @@
         <v>128562925</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128564240</v>
+        <v>128565676</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537145</v>
+        <v>537263</v>
       </c>
       <c r="R33" t="n">
-        <v>6983943</v>
+        <v>6983976</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,7 +4072,7 @@
         <v>128565042</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>128564077</v>
       </c>
       <c r="B35" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R37" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R38" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,7 +4607,7 @@
         <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128568213</v>
+        <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537231</v>
+        <v>537276</v>
       </c>
       <c r="R40" t="n">
-        <v>6983882</v>
+        <v>6983912</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R41" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R16" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R17" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
         <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R22" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R23" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128564240</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537145</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983943</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128562925</v>
+        <v>128564240</v>
       </c>
       <c r="B31" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537100</v>
+        <v>537145</v>
       </c>
       <c r="R31" t="n">
-        <v>6983903</v>
+        <v>6983943</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B32" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R32" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565676</v>
+        <v>128565808</v>
       </c>
       <c r="B33" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537263</v>
+        <v>537271</v>
       </c>
       <c r="R33" t="n">
-        <v>6983976</v>
+        <v>6983985</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128565042</v>
+        <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537218</v>
+        <v>537145</v>
       </c>
       <c r="R34" t="n">
-        <v>6983991</v>
+        <v>6983958</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128564077</v>
+        <v>128565042</v>
       </c>
       <c r="B35" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537145</v>
+        <v>537218</v>
       </c>
       <c r="R35" t="n">
-        <v>6983958</v>
+        <v>6983991</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4393,7 +4393,7 @@
         <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R16" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R17" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3534,32 +3534,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128564240</v>
       </c>
       <c r="B29" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537145</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983943</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128562925</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537100</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983903</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128564240</v>
+        <v>128565808</v>
       </c>
       <c r="B31" t="n">
         <v>98591</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537145</v>
+        <v>537271</v>
       </c>
       <c r="R31" t="n">
-        <v>6983943</v>
+        <v>6983985</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128562925</v>
+        <v>128565676</v>
       </c>
       <c r="B32" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537100</v>
+        <v>537263</v>
       </c>
       <c r="R32" t="n">
-        <v>6983903</v>
+        <v>6983976</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565808</v>
+        <v>128562964</v>
       </c>
       <c r="B33" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537271</v>
+        <v>537107</v>
       </c>
       <c r="R33" t="n">
-        <v>6983985</v>
+        <v>6983905</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R35" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128563502</v>
+        <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537130</v>
+        <v>537218</v>
       </c>
       <c r="R36" t="n">
-        <v>6983903</v>
+        <v>6983991</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B18" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R18" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R19" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128564240</v>
+        <v>128562964</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537145</v>
+        <v>537107</v>
       </c>
       <c r="R29" t="n">
-        <v>6983943</v>
+        <v>6983905</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562925</v>
+        <v>128564240</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537100</v>
+        <v>537145</v>
       </c>
       <c r="R30" t="n">
-        <v>6983903</v>
+        <v>6983943</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B31" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R31" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128565676</v>
+        <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537263</v>
+        <v>537271</v>
       </c>
       <c r="R32" t="n">
-        <v>6983976</v>
+        <v>6983985</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B33" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R33" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4286,7 +4286,7 @@
         <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R13" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R14" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R18" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R19" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>80221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128564240</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>98592</v>
+        <v>57876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537145</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983943</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128562925</v>
+        <v>128564240</v>
       </c>
       <c r="B31" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537100</v>
+        <v>537145</v>
       </c>
       <c r="R31" t="n">
-        <v>6983903</v>
+        <v>6983943</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B32" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R32" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565676</v>
+        <v>128565808</v>
       </c>
       <c r="B33" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537263</v>
+        <v>537271</v>
       </c>
       <c r="R33" t="n">
-        <v>6983976</v>
+        <v>6983985</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,7 +4072,7 @@
         <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567360</v>
+        <v>128567506</v>
       </c>
       <c r="B39" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537297</v>
+        <v>537276</v>
       </c>
       <c r="R39" t="n">
-        <v>6983900</v>
+        <v>6983912</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R40" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568213</v>
+        <v>128567360</v>
       </c>
       <c r="B41" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537231</v>
+        <v>537297</v>
       </c>
       <c r="R41" t="n">
-        <v>6983882</v>
+        <v>6983900</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R13" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R14" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B22" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R22" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R23" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567506</v>
+        <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537276</v>
+        <v>537297</v>
       </c>
       <c r="R39" t="n">
-        <v>6983912</v>
+        <v>6983900</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,7 +4711,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128568213</v>
+        <v>128567506</v>
       </c>
       <c r="B40" t="n">
         <v>98619</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537231</v>
+        <v>537276</v>
       </c>
       <c r="R40" t="n">
-        <v>6983882</v>
+        <v>6983912</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567360</v>
+        <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537297</v>
+        <v>537231</v>
       </c>
       <c r="R41" t="n">
-        <v>6983900</v>
+        <v>6983882</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R18" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R19" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,7 +3002,7 @@
         <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128564240</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>128562925</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>128565808</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R18" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R19" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R22" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B23" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R23" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128564408</v>
+        <v>128567227</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537155</v>
+        <v>537292</v>
       </c>
       <c r="R24" t="n">
-        <v>6983961</v>
+        <v>6983911</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128564188</v>
+        <v>128564408</v>
       </c>
       <c r="B25" t="n">
         <v>80225</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537140</v>
+        <v>537155</v>
       </c>
       <c r="R25" t="n">
-        <v>6983933</v>
+        <v>6983961</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128567227</v>
+        <v>128564188</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537292</v>
+        <v>537140</v>
       </c>
       <c r="R26" t="n">
-        <v>6983911</v>
+        <v>6983933</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,7 +3323,7 @@
         <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128564240</v>
       </c>
       <c r="B29" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537145</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983943</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128562925</v>
       </c>
       <c r="B30" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537100</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983903</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128564240</v>
+        <v>128565808</v>
       </c>
       <c r="B31" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537145</v>
+        <v>537271</v>
       </c>
       <c r="R31" t="n">
-        <v>6983943</v>
+        <v>6983985</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128562925</v>
+        <v>128565676</v>
       </c>
       <c r="B32" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537100</v>
+        <v>537263</v>
       </c>
       <c r="R32" t="n">
-        <v>6983903</v>
+        <v>6983976</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565808</v>
+        <v>128562964</v>
       </c>
       <c r="B33" t="n">
-        <v>98625</v>
+        <v>57876</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537271</v>
+        <v>537107</v>
       </c>
       <c r="R33" t="n">
-        <v>6983985</v>
+        <v>6983905</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4286,7 +4286,7 @@
         <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567360</v>
+        <v>128567506</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537297</v>
+        <v>537276</v>
       </c>
       <c r="R39" t="n">
-        <v>6983900</v>
+        <v>6983912</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R40" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568213</v>
+        <v>128567360</v>
       </c>
       <c r="B41" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537231</v>
+        <v>537297</v>
       </c>
       <c r="R41" t="n">
-        <v>6983882</v>
+        <v>6983900</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B8" t="n">
         <v>98632</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R8" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B9" t="n">
         <v>98632</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R9" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B10" t="n">
         <v>98632</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R10" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B11" t="n">
         <v>98632</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R11" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B18" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R18" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R19" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B27" t="n">
         <v>98632</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R27" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B28" t="n">
         <v>98632</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R28" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,32 +3534,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128564240</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537145</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983943</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562925</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537100</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983903</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B31" t="n">
         <v>98632</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R31" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,32 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128565676</v>
+        <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537263</v>
+        <v>537271</v>
       </c>
       <c r="R32" t="n">
-        <v>6983976</v>
+        <v>6983985</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128562964</v>
+        <v>128564240</v>
       </c>
       <c r="B33" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537107</v>
+        <v>537145</v>
       </c>
       <c r="R33" t="n">
-        <v>6983905</v>
+        <v>6983943</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B37" t="n">
         <v>98632</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R37" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B38" t="n">
         <v>98632</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R38" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567506</v>
+        <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537276</v>
+        <v>537297</v>
       </c>
       <c r="R39" t="n">
-        <v>6983912</v>
+        <v>6983900</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567360</v>
+        <v>128567506</v>
       </c>
       <c r="B41" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537297</v>
+        <v>537276</v>
       </c>
       <c r="R41" t="n">
-        <v>6983900</v>
+        <v>6983912</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128567227</v>
+        <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537292</v>
+        <v>537155</v>
       </c>
       <c r="R24" t="n">
-        <v>6983911</v>
+        <v>6983961</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128564408</v>
+        <v>128564188</v>
       </c>
       <c r="B25" t="n">
         <v>80225</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537155</v>
+        <v>537140</v>
       </c>
       <c r="R25" t="n">
-        <v>6983961</v>
+        <v>6983933</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128564188</v>
+        <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537140</v>
+        <v>537292</v>
       </c>
       <c r="R26" t="n">
-        <v>6983933</v>
+        <v>6983911</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R8" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R9" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R10" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R11" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R18" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R19" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R22" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R23" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,7 +3002,7 @@
         <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R27" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R28" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128562964</v>
       </c>
       <c r="B29" t="n">
-        <v>80225</v>
+        <v>57880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537107</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983905</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128564240</v>
       </c>
       <c r="B30" t="n">
-        <v>57876</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537145</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983943</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,7 +3751,7 @@
         <v>128562925</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128564240</v>
+        <v>128565676</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537145</v>
+        <v>537263</v>
       </c>
       <c r="R33" t="n">
-        <v>6983943</v>
+        <v>6983976</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4072,7 +4072,7 @@
         <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R37" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R38" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,7 +4607,7 @@
         <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128568213</v>
+        <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537231</v>
+        <v>537276</v>
       </c>
       <c r="R40" t="n">
-        <v>6983882</v>
+        <v>6983912</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R41" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R8" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R9" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R13" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R14" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R18" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R19" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128564408</v>
+        <v>128567227</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537155</v>
+        <v>537292</v>
       </c>
       <c r="R24" t="n">
-        <v>6983961</v>
+        <v>6983911</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128564188</v>
+        <v>128564408</v>
       </c>
       <c r="B25" t="n">
         <v>80229</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537140</v>
+        <v>537155</v>
       </c>
       <c r="R25" t="n">
-        <v>6983933</v>
+        <v>6983961</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128567227</v>
+        <v>128564188</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537292</v>
+        <v>537140</v>
       </c>
       <c r="R26" t="n">
-        <v>6983911</v>
+        <v>6983933</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B27" t="n">
         <v>98636</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R27" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B28" t="n">
         <v>98636</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R28" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>57880</v>
+        <v>80229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128564240</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>57880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537145</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983943</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128562925</v>
+        <v>128564240</v>
       </c>
       <c r="B31" t="n">
         <v>98636</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537100</v>
+        <v>537145</v>
       </c>
       <c r="R31" t="n">
-        <v>6983903</v>
+        <v>6983943</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B32" t="n">
         <v>98636</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R32" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565676</v>
+        <v>128565808</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537263</v>
+        <v>537271</v>
       </c>
       <c r="R33" t="n">
-        <v>6983976</v>
+        <v>6983985</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128564077</v>
+        <v>128563502</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>57880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537145</v>
+        <v>537130</v>
       </c>
       <c r="R34" t="n">
-        <v>6983958</v>
+        <v>6983903</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128563502</v>
+        <v>128564077</v>
       </c>
       <c r="B35" t="n">
-        <v>57880</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537130</v>
+        <v>537145</v>
       </c>
       <c r="R35" t="n">
-        <v>6983903</v>
+        <v>6983958</v>
       </c>
       <c r="S35" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R8" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R9" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R16" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R17" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R18" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R19" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B27" t="n">
         <v>98636</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R27" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B28" t="n">
         <v>98636</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R28" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128563502</v>
+        <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>57880</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537130</v>
+        <v>537145</v>
       </c>
       <c r="R34" t="n">
-        <v>6983903</v>
+        <v>6983958</v>
       </c>
       <c r="S34" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128564077</v>
+        <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>57880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537145</v>
+        <v>537130</v>
       </c>
       <c r="R35" t="n">
-        <v>6983958</v>
+        <v>6983903</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567360</v>
+        <v>128567506</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537297</v>
+        <v>537276</v>
       </c>
       <c r="R39" t="n">
-        <v>6983900</v>
+        <v>6983912</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,7 +4711,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B40" t="n">
         <v>98636</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R40" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568213</v>
+        <v>128567360</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537231</v>
+        <v>537297</v>
       </c>
       <c r="R41" t="n">
-        <v>6983882</v>
+        <v>6983900</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128566784</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>128563380</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>128563099</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128562997</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R13" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R14" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128567589</v>
+        <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537289</v>
+        <v>537169</v>
       </c>
       <c r="R16" t="n">
-        <v>6983869</v>
+        <v>6983991</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,32 +2250,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128564364</v>
+        <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537169</v>
+        <v>537289</v>
       </c>
       <c r="R17" t="n">
-        <v>6983991</v>
+        <v>6983869</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,7 +2360,7 @@
         <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128567227</v>
+        <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537292</v>
+        <v>537155</v>
       </c>
       <c r="R24" t="n">
-        <v>6983911</v>
+        <v>6983961</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128564408</v>
+        <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537155</v>
+        <v>537140</v>
       </c>
       <c r="R25" t="n">
-        <v>6983961</v>
+        <v>6983933</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128564188</v>
+        <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537140</v>
+        <v>537292</v>
       </c>
       <c r="R26" t="n">
-        <v>6983933</v>
+        <v>6983911</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,7 +3323,7 @@
         <v>128562753</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128566515</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128564240</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>128562925</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>128565808</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128563502</v>
+        <v>128565042</v>
       </c>
       <c r="B35" t="n">
-        <v>57880</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537130</v>
+        <v>537218</v>
       </c>
       <c r="R35" t="n">
-        <v>6983903</v>
+        <v>6983991</v>
       </c>
       <c r="S35" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R36" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4393,7 +4393,7 @@
         <v>128566475</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>128563582</v>
       </c>
       <c r="B38" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>128567506</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>128568213</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>128567360</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R8" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B9" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R9" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B10" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R10" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B11" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R11" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B13" t="n">
-        <v>80134</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R13" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>80139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R14" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>80139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80134</v>
+        <v>98651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128564408</v>
+        <v>128567227</v>
       </c>
       <c r="B24" t="n">
-        <v>80134</v>
+        <v>98651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537155</v>
+        <v>537292</v>
       </c>
       <c r="R24" t="n">
-        <v>6983961</v>
+        <v>6983911</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128567227</v>
+        <v>128564408</v>
       </c>
       <c r="B26" t="n">
-        <v>98646</v>
+        <v>80139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537292</v>
+        <v>537155</v>
       </c>
       <c r="R26" t="n">
-        <v>6983911</v>
+        <v>6983961</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B27" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R27" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B28" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R28" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128565676</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>80134</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537263</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983976</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128564240</v>
+        <v>128562925</v>
       </c>
       <c r="B31" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537145</v>
+        <v>537100</v>
       </c>
       <c r="R31" t="n">
-        <v>6983943</v>
+        <v>6983903</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128562925</v>
+        <v>128565808</v>
       </c>
       <c r="B32" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537100</v>
+        <v>537271</v>
       </c>
       <c r="R32" t="n">
-        <v>6983903</v>
+        <v>6983985</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565808</v>
+        <v>128564240</v>
       </c>
       <c r="B33" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537271</v>
+        <v>537145</v>
       </c>
       <c r="R33" t="n">
-        <v>6983985</v>
+        <v>6983943</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,32 +4069,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128565042</v>
+        <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>98646</v>
+        <v>80139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537218</v>
+        <v>537145</v>
       </c>
       <c r="R34" t="n">
-        <v>6983991</v>
+        <v>6983958</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128564077</v>
+        <v>128565042</v>
       </c>
       <c r="B35" t="n">
-        <v>80134</v>
+        <v>98651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537145</v>
+        <v>537218</v>
       </c>
       <c r="R35" t="n">
-        <v>6983958</v>
+        <v>6983991</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B37" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R37" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B38" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R38" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567360</v>
+        <v>128568213</v>
       </c>
       <c r="B39" t="n">
-        <v>80134</v>
+        <v>98651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537297</v>
+        <v>537231</v>
       </c>
       <c r="R39" t="n">
-        <v>6983900</v>
+        <v>6983882</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4714,7 +4714,7 @@
         <v>128567506</v>
       </c>
       <c r="B40" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568213</v>
+        <v>128567360</v>
       </c>
       <c r="B41" t="n">
-        <v>98646</v>
+        <v>80139</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537231</v>
+        <v>537297</v>
       </c>
       <c r="R41" t="n">
-        <v>6983882</v>
+        <v>6983900</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B8" t="n">
         <v>98651</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R8" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B9" t="n">
         <v>98651</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R9" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B10" t="n">
         <v>98651</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R10" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B11" t="n">
         <v>98651</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R11" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128567227</v>
+        <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537292</v>
+        <v>537155</v>
       </c>
       <c r="R24" t="n">
-        <v>6983911</v>
+        <v>6983961</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128564408</v>
+        <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>80139</v>
+        <v>98651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537155</v>
+        <v>537292</v>
       </c>
       <c r="R26" t="n">
-        <v>6983961</v>
+        <v>6983911</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B27" t="n">
         <v>98651</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R27" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B28" t="n">
         <v>98651</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R28" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128562925</v>
+        <v>128564240</v>
       </c>
       <c r="B31" t="n">
         <v>98651</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537100</v>
+        <v>537145</v>
       </c>
       <c r="R31" t="n">
-        <v>6983903</v>
+        <v>6983943</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B32" t="n">
         <v>98651</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R32" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128564240</v>
+        <v>128565808</v>
       </c>
       <c r="B33" t="n">
         <v>98651</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537145</v>
+        <v>537271</v>
       </c>
       <c r="R33" t="n">
-        <v>6983943</v>
+        <v>6983985</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128564077</v>
+        <v>128563502</v>
       </c>
       <c r="B34" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537145</v>
+        <v>537130</v>
       </c>
       <c r="R34" t="n">
-        <v>6983958</v>
+        <v>6983903</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128563502</v>
+        <v>128564077</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537130</v>
+        <v>537145</v>
       </c>
       <c r="R36" t="n">
-        <v>6983903</v>
+        <v>6983958</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B37" t="n">
         <v>98651</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R37" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B38" t="n">
         <v>98651</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R38" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128568213</v>
+        <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537231</v>
+        <v>537297</v>
       </c>
       <c r="R39" t="n">
-        <v>6983882</v>
+        <v>6983900</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567360</v>
+        <v>128568213</v>
       </c>
       <c r="B41" t="n">
-        <v>80139</v>
+        <v>98651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537297</v>
+        <v>537231</v>
       </c>
       <c r="R41" t="n">
-        <v>6983900</v>
+        <v>6983882</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R8" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R9" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R10" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R11" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1718,7 @@
         <v>128567714</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R13" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R14" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,7 +2039,7 @@
         <v>128563814</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>128564364</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128567589</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R18" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R19" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,7 +2574,7 @@
         <v>128568010</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128568394</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R22" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R23" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,7 +3002,7 @@
         <v>128564408</v>
       </c>
       <c r="B24" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128564188</v>
       </c>
       <c r="B25" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128567227</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R27" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R28" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128562964</v>
       </c>
       <c r="B29" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537107</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983905</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128562925</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537100</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983903</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128564240</v>
+        <v>128565808</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537145</v>
+        <v>537271</v>
       </c>
       <c r="R31" t="n">
-        <v>6983943</v>
+        <v>6983985</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128562925</v>
+        <v>128564240</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537100</v>
+        <v>537145</v>
       </c>
       <c r="R32" t="n">
-        <v>6983903</v>
+        <v>6983943</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565808</v>
+        <v>128565676</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537271</v>
+        <v>537263</v>
       </c>
       <c r="R33" t="n">
-        <v>6983985</v>
+        <v>6983976</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128563502</v>
+        <v>128564077</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4080,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537130</v>
+        <v>537145</v>
       </c>
       <c r="R34" t="n">
-        <v>6983903</v>
+        <v>6983958</v>
       </c>
       <c r="S34" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4179,7 +4179,7 @@
         <v>128565042</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128564077</v>
+        <v>128563502</v>
       </c>
       <c r="B36" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4294,21 +4294,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537145</v>
+        <v>537130</v>
       </c>
       <c r="R36" t="n">
-        <v>6983958</v>
+        <v>6983903</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R37" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R38" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,7 +4607,7 @@
         <v>128567360</v>
       </c>
       <c r="B39" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128567506</v>
+        <v>128568213</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537276</v>
+        <v>537231</v>
       </c>
       <c r="R40" t="n">
-        <v>6983912</v>
+        <v>6983882</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128568213</v>
+        <v>128567506</v>
       </c>
       <c r="B41" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537231</v>
+        <v>537276</v>
       </c>
       <c r="R41" t="n">
-        <v>6983882</v>
+        <v>6983912</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4928,7 +4928,7 @@
         <v>128564451</v>
       </c>
       <c r="B42" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -2357,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128567077</v>
+        <v>128565305</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537265</v>
+        <v>537228</v>
       </c>
       <c r="R18" t="n">
-        <v>6983926</v>
+        <v>6983979</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128565305</v>
+        <v>128567077</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537228</v>
+        <v>537265</v>
       </c>
       <c r="R19" t="n">
-        <v>6983979</v>
+        <v>6983926</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128563551</v>
+        <v>128567544</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537139</v>
+        <v>537293</v>
       </c>
       <c r="R22" t="n">
-        <v>6983908</v>
+        <v>6983882</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,32 +2892,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128567544</v>
+        <v>128563551</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537293</v>
+        <v>537139</v>
       </c>
       <c r="R23" t="n">
-        <v>6983882</v>
+        <v>6983908</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128562964</v>
+        <v>128565676</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537107</v>
+        <v>537263</v>
       </c>
       <c r="R29" t="n">
-        <v>6983905</v>
+        <v>6983976</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562925</v>
+        <v>128562964</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537100</v>
+        <v>537107</v>
       </c>
       <c r="R30" t="n">
-        <v>6983903</v>
+        <v>6983905</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128565808</v>
+        <v>128562925</v>
       </c>
       <c r="B31" t="n">
         <v>98659</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537271</v>
+        <v>537100</v>
       </c>
       <c r="R31" t="n">
-        <v>6983985</v>
+        <v>6983903</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128564240</v>
+        <v>128565808</v>
       </c>
       <c r="B32" t="n">
         <v>98659</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537145</v>
+        <v>537271</v>
       </c>
       <c r="R32" t="n">
-        <v>6983943</v>
+        <v>6983985</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128565676</v>
+        <v>128564240</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537263</v>
+        <v>537145</v>
       </c>
       <c r="R33" t="n">
-        <v>6983976</v>
+        <v>6983943</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 22143-2025 artfynd.xlsx
+++ b/artfynd/A 22143-2025 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128563380</v>
+        <v>128566784</v>
       </c>
       <c r="B8" t="n">
         <v>98659</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537130</v>
+        <v>537255</v>
       </c>
       <c r="R8" t="n">
-        <v>6983903</v>
+        <v>6983933</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128566784</v>
+        <v>128563380</v>
       </c>
       <c r="B9" t="n">
         <v>98659</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537255</v>
+        <v>537130</v>
       </c>
       <c r="R9" t="n">
-        <v>6983933</v>
+        <v>6983903</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128562997</v>
+        <v>128563099</v>
       </c>
       <c r="B10" t="n">
         <v>98659</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537107</v>
+        <v>537112</v>
       </c>
       <c r="R10" t="n">
-        <v>6983905</v>
+        <v>6983914</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128563099</v>
+        <v>128562997</v>
       </c>
       <c r="B11" t="n">
         <v>98659</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537112</v>
+        <v>537107</v>
       </c>
       <c r="R11" t="n">
-        <v>6983914</v>
+        <v>6983905</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128567670</v>
+        <v>128566920</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537282</v>
+        <v>537279</v>
       </c>
       <c r="R13" t="n">
-        <v>6983918</v>
+        <v>6983922</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,32 +1929,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128566920</v>
+        <v>128567670</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537279</v>
+        <v>537282</v>
       </c>
       <c r="R14" t="n">
-        <v>6983922</v>
+        <v>6983918</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128564408</v>
+        <v>128567227</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537155</v>
+        <v>537292</v>
       </c>
       <c r="R24" t="n">
-        <v>6983961</v>
+        <v>6983911</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128564188</v>
+        <v>128564408</v>
       </c>
       <c r="B25" t="n">
         <v>80140</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537140</v>
+        <v>537155</v>
       </c>
       <c r="R25" t="n">
-        <v>6983933</v>
+        <v>6983961</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,32 +3213,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128567227</v>
+        <v>128564188</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537292</v>
+        <v>537140</v>
       </c>
       <c r="R26" t="n">
-        <v>6983911</v>
+        <v>6983933</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128566515</v>
+        <v>128562753</v>
       </c>
       <c r="B27" t="n">
         <v>98659</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537248</v>
+        <v>537089</v>
       </c>
       <c r="R27" t="n">
-        <v>6983943</v>
+        <v>6983899</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128562753</v>
+        <v>128566515</v>
       </c>
       <c r="B28" t="n">
         <v>98659</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537089</v>
+        <v>537248</v>
       </c>
       <c r="R28" t="n">
-        <v>6983899</v>
+        <v>6983943</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128565676</v>
+        <v>128562964</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537263</v>
+        <v>537107</v>
       </c>
       <c r="R29" t="n">
-        <v>6983976</v>
+        <v>6983905</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,32 +3641,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128562964</v>
+        <v>128564240</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537107</v>
+        <v>537145</v>
       </c>
       <c r="R30" t="n">
-        <v>6983905</v>
+        <v>6983943</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128564240</v>
+        <v>128565676</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537145</v>
+        <v>537263</v>
       </c>
       <c r="R33" t="n">
-        <v>6983943</v>
+        <v>6983976</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4176,32 +4176,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128565042</v>
+        <v>128563502</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537218</v>
+        <v>537130</v>
       </c>
       <c r="R35" t="n">
-        <v>6983991</v>
+        <v>6983903</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128563502</v>
+        <v>128565042</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537130</v>
+        <v>537218</v>
       </c>
       <c r="R36" t="n">
-        <v>6983903</v>
+        <v>6983991</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128563582</v>
+        <v>128566475</v>
       </c>
       <c r="B37" t="n">
         <v>98659</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537142</v>
+        <v>537259</v>
       </c>
       <c r="R37" t="n">
-        <v>6983916</v>
+        <v>6983948</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128566475</v>
+        <v>128563582</v>
       </c>
       <c r="B38" t="n">
         <v>98659</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537259</v>
+        <v>537142</v>
       </c>
       <c r="R38" t="n">
-        <v>6983948</v>
+        <v>6983916</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,32 +4604,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128567360</v>
+        <v>128567506</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537297</v>
+        <v>537276</v>
       </c>
       <c r="R39" t="n">
-        <v>6983900</v>
+        <v>6983912</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4818,32 +4818,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128567506</v>
+        <v>128567360</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537276</v>
+        <v>537297</v>
       </c>
       <c r="R41" t="n">
-        <v>6983912</v>
+        <v>6983900</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
